--- a/portfolio_260531_FIN.XLSX
+++ b/portfolio_260531_FIN.XLSX
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meritzam\Desktop\3.AA\1.Main\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kcgi\Desktop\5월\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11955" activeTab="1"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11955"/>
   </bookViews>
   <sheets>
     <sheet name="Investment Weight" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Price Aggressive" sheetId="4" r:id="rId4"/>
     <sheet name="Price Conservative " sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913" calcMode="manual"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -255,7 +255,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
     <numFmt numFmtId="178" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    <numFmt numFmtId="180" formatCode="0.0000"/>
+    <numFmt numFmtId="179" formatCode="0.0000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -362,12 +362,12 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1615,16 +1615,16 @@
       <c r="G2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="15">
         <v>0.2</v>
       </c>
-      <c r="I2" s="17">
+      <c r="I2" s="15">
         <v>9.2948251734221508</v>
       </c>
-      <c r="J2" s="17">
+      <c r="J2" s="15">
         <v>13.761348587214091</v>
       </c>
-      <c r="K2" s="17">
+      <c r="K2" s="15">
         <v>29.522061202566238</v>
       </c>
     </row>
@@ -1650,16 +1650,16 @@
       <c r="G3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="15">
         <v>0.2</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="15">
         <v>7.8265853082965187</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="15">
         <v>11.4867665217526</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="15">
         <v>24.966659225893959</v>
       </c>
     </row>
@@ -1685,16 +1685,16 @@
       <c r="G4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="16">
         <v>0.2</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="16">
         <v>5.1371711529886621</v>
       </c>
-      <c r="J4" s="18">
+      <c r="J4" s="16">
         <v>7.6750962822055957</v>
       </c>
-      <c r="K4" s="18">
+      <c r="K4" s="16">
         <v>17.332926894341941</v>
       </c>
     </row>
@@ -1720,16 +1720,16 @@
       <c r="G5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="16">
         <v>1.2</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="16">
         <v>6.6664054694693053</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="16">
         <v>4.961563480197273</v>
       </c>
-      <c r="K5" s="18">
+      <c r="K5" s="16">
         <v>15.69783300841412</v>
       </c>
     </row>
@@ -1755,16 +1755,16 @@
       <c r="G6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="16">
         <v>3.8</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="16">
         <v>1.63631398743882</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="16">
         <v>-0.6922452500630949</v>
       </c>
-      <c r="K6" s="18">
+      <c r="K6" s="16">
         <v>10.22981857473018</v>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -61321,11 +61321,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -63129,11 +63129,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
